--- a/api/1/clv3/xlsx/fr/ReportingOrganisation.xlsx
+++ b/api/1/clv3/xlsx/fr/ReportingOrganisation.xlsx
@@ -31,12 +31,12 @@
     <t>codeforiati:hq-country-or-region</t>
   </si>
   <si>
+    <t>codeforiati:organisation-type</t>
+  </si>
+  <si>
     <t>codeforiati:organisation-type-code</t>
   </si>
   <si>
-    <t>codeforiati:organisation-type</t>
-  </si>
-  <si>
     <t>AU-5</t>
   </si>
   <si>
@@ -52,12 +52,12 @@
     <t>Australia</t>
   </si>
   <si>
+    <t>Government</t>
+  </si>
+  <si>
     <t>10</t>
   </si>
   <si>
-    <t>Government</t>
-  </si>
-  <si>
     <t>44000</t>
   </si>
   <si>
@@ -70,12 +70,12 @@
     <t>(No country assigned)</t>
   </si>
   <si>
+    <t>Multilateral</t>
+  </si>
+  <si>
     <t>40</t>
   </si>
   <si>
-    <t>Multilateral</t>
-  </si>
-  <si>
     <t>US-EIN-941655673</t>
   </si>
   <si>
@@ -88,12 +88,12 @@
     <t>United States</t>
   </si>
   <si>
+    <t>Foundation</t>
+  </si>
+  <si>
     <t>60</t>
   </si>
   <si>
-    <t>Foundation</t>
-  </si>
-  <si>
     <t>41AAA</t>
   </si>
   <si>
@@ -115,12 +115,12 @@
     <t>United Kingdom</t>
   </si>
   <si>
+    <t>International NGO</t>
+  </si>
+  <si>
     <t>21</t>
   </si>
   <si>
-    <t>International NGO</t>
-  </si>
-  <si>
     <t>XI-IATI-EC_INTPA</t>
   </si>
   <si>
@@ -130,12 +130,12 @@
     <t>ec-intpa</t>
   </si>
   <si>
+    <t>Other Public Sector</t>
+  </si>
+  <si>
     <t>15</t>
   </si>
   <si>
-    <t>Other Public Sector</t>
-  </si>
-  <si>
     <t>XI-IATI-EC_DEVCO</t>
   </si>
   <si>
@@ -310,12 +310,12 @@
     <t>gavi</t>
   </si>
   <si>
+    <t>Public Private Partnership</t>
+  </si>
+  <si>
     <t>30</t>
   </si>
   <si>
-    <t>Public Private Partnership</t>
-  </si>
-  <si>
     <t>US-EIN-300108263</t>
   </si>
   <si>
@@ -382,12 +382,12 @@
     <t>Nepal</t>
   </si>
   <si>
+    <t>Academic, Training and Research</t>
+  </si>
+  <si>
     <t>80</t>
   </si>
   <si>
-    <t>Academic, Training and Research</t>
-  </si>
-  <si>
     <t>GB-CHC-327421</t>
   </si>
   <si>
@@ -544,12 +544,12 @@
     <t>icauk</t>
   </si>
   <si>
+    <t>National NGO</t>
+  </si>
+  <si>
     <t>22</t>
   </si>
   <si>
-    <t>National NGO</t>
-  </si>
-  <si>
     <t>GB-CHC-298316</t>
   </si>
   <si>
@@ -889,12 +889,12 @@
     <t>South Africa</t>
   </si>
   <si>
+    <t>Regional NGO</t>
+  </si>
+  <si>
     <t>23</t>
   </si>
   <si>
-    <t>Regional NGO</t>
-  </si>
-  <si>
     <t>CH-FDJP-CHE-110347351</t>
   </si>
   <si>
@@ -1186,10 +1186,10 @@
     <t>tripleline_crownagents</t>
   </si>
   <si>
+    <t>Private Sector</t>
+  </si>
+  <si>
     <t>70</t>
-  </si>
-  <si>
-    <t>Private Sector</t>
   </si>
   <si>
     <t>GB-CHC-1058991</t>
